--- a/students/رسولیtop1.3ok.xlsx
+++ b/students/رسولیtop1.3ok.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52866523-77D7-4E8E-AEE1-5E20B493C0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -120,12 +121,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -194,21 +195,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,25 +479,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.296875" customWidth="1"/>
+    <col min="5" max="5" width="13.296875" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" customWidth="1"/>
+    <col min="7" max="7" width="41.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>11489</v>
       </c>
@@ -543,8 +541,8 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>111333</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -564,162 +562,157 @@
       </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>10822</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="8">
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="6">
         <v>9196956796</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="6">
         <v>9193479691</v>
       </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
         <v>10937</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5">
         <v>9372832881</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5">
         <v>9364838557</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>10223</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="6">
         <v>9100231667</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>9196743521</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>10421</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7">
         <v>9191434779</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7">
         <v>9191417832</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>10422</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>9191434779</v>
+      </c>
+      <c r="F8">
+        <v>9191417832</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>10096</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
         <v>9118412811</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9">
         <v>9191414825</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>111964</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="7">
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10">
         <v>9128416595</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>111101</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="7">
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11">
         <v>9127426232</v>
       </c>
       <c r="F11">
@@ -729,57 +722,57 @@
         <v>9016839755</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>111296</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="7">
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12">
         <v>9193415359</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>111609</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="7">
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13">
         <v>9385276989</v>
       </c>
       <c r="F13">
         <v>9127428950</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>111660</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="7">
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14">
         <v>9190605560</v>
       </c>
       <c r="F14">
